--- a/evaluation_forms/027_hanaro_progress_sheet_report_template--evaluation_forms.xlsx
+++ b/evaluation_forms/027_hanaro_progress_sheet_report_template--evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -554,7 +554,7 @@
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -577,7 +577,7 @@
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -600,7 +600,7 @@
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -623,7 +623,7 @@
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -646,7 +646,7 @@
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -738,7 +738,7 @@
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -761,7 +761,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -830,283 +830,7 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>student_name</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Student Name</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>student_id</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Student ID</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>teacher_name</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Teacher Name</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>reading_progress</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Reading Progress</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>listening_progress</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Listening Progress</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>understand_teachers_dscussions</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Understand Teachers Discussions</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>reading_progress_notes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Reading Progress Notes</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>listening_progress_notes</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Listening Progress Notes</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>reading_progress_email</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Reading Progress Email</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>listening_progress_email</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Listening Progress Email</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>progress_sheet_date</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Progress Sheet Date</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>progress_sheet_time</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Progress Sheet Time</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1121,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1447,210 +1171,6 @@
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>reading_progress_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>reading_progress_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>reading_progress_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>reading_progress_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>listening_progress_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>listening_progress_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>listening_progress_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>listening_progress_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Poor</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>understand_teachers_dscussions_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>excellent</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Excellent</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>understand_teachers_dscussions_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>good</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Good</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>understand_teachers_dscussions_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>fair</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Fair</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>understand_teachers_dscussions_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>poor</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
         <is>
           <t>Poor</t>
         </is>
